--- a/data/gravel/T-Lab X3 2025.xlsx
+++ b/data/gravel/T-Lab X3 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058BE344-E8C4-1D47-97F4-4B2DC4291C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FBD38A-BC46-B043-9247-ED5AB10EFBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="600" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>a8:h34</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -704,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1382,9 +1400,6 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C35" s="5">
         <v>60</v>
       </c>
@@ -1409,7 +1424,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C36" s="1">
         <v>64</v>
@@ -1432,10 +1447,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>87</v>
@@ -1458,192 +1473,219 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>32</v>
+        <v>107</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="1">
-        <v>50</v>
+        <v>109</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="B43" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="1">
-        <v>3550</v>
+        <v>58</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="1">
-        <v>4600</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>65</v>
       </c>
     </row>

--- a/data/gravel/T-Lab X3 2025.xlsx
+++ b/data/gravel/T-Lab X3 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FBD38A-BC46-B043-9247-ED5AB10EFBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589314C0-88A6-5845-A7AE-A16B62736660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -342,9 +342,6 @@
   </si>
   <si>
     <t>Chain Stay Length</t>
-  </si>
-  <si>
-    <t>no</t>
   </si>
   <si>
     <t>a8:h34</t>
@@ -775,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1447,10 +1444,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>87</v>
@@ -1473,18 +1470,18 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1574,7 +1571,7 @@
         <v>45</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/T-Lab X3 2025.xlsx
+++ b/data/gravel/T-Lab X3 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589314C0-88A6-5845-A7AE-A16B62736660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A26497A-B12D-A24D-87DF-BD6ED9F988FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://tlab-bike.transforms.svdcdn.com/production/upload/images/X3fi_side.jpg?w=1600&amp;q=80&amp;auto=format&amp;fit=crop&amp;crop=focalpoint&amp;fp-x=0.5&amp;fp-y=0.5&amp;dm=1741375385&amp;s=dbae0a5b58fd0bc78358506bbcd910d8</t>
   </si>
 </sst>
 </file>
@@ -767,6 +770,11 @@
         <v>79</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/T-Lab X3 2025.xlsx
+++ b/data/gravel/T-Lab X3 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A26497A-B12D-A24D-87DF-BD6ED9F988FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F8807A-C442-7E48-8119-C5E8B523D270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,15 @@
   </si>
   <si>
     <t>https://tlab-bike.transforms.svdcdn.com/production/upload/images/X3fi_side.jpg?w=1600&amp;q=80&amp;auto=format&amp;fit=crop&amp;crop=focalpoint&amp;fp-x=0.5&amp;fp-y=0.5&amp;dm=1741375385&amp;s=dbae0a5b58fd0bc78358506bbcd910d8</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Montreal, Québec, Canada</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -722,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1693,6 +1702,17 @@
       <c r="A74" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="B74" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/T-Lab X3 2025.xlsx
+++ b/data/gravel/T-Lab X3 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F8807A-C442-7E48-8119-C5E8B523D270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FABA18-6161-4841-88B1-56054597D7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -731,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1567,150 +1585,180 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1">
-        <v>3550</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="1">
-        <v>4600</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="1">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>112</v>
       </c>
     </row>
